--- a/docs/dga/نموذج الالتزام - منصة الشهادات الاحترافية - جامعة شقراء.xlsx
+++ b/docs/dga/نموذج الالتزام - منصة الشهادات الاحترافية - جامعة شقراء.xlsx
@@ -1796,21 +1796,25 @@
       <c r="F20" s="149" t="n"/>
       <c r="G20" s="133" t="inlineStr">
         <is>
-          <t>تطبيق جزئي</t>
-        </is>
-      </c>
-      <c r="H20" s="45" t="n"/>
+          <t>تطبيق كلي</t>
+        </is>
+      </c>
+      <c r="H20" s="150" t="inlineStr">
+        <is>
+          <t>public/website/js/dga-icons.js</t>
+        </is>
+      </c>
       <c r="I20" s="152" t="inlineStr">
         <is>
-          <t>الأيقونات خطية (stroke) بأحجام 16/20/24px وبألوان محايدة، وألوان الحالات للتنبيهات فقط، والأيقونات الكبيرة بصيغة Featured icon (48px بخلفية خفيفة).</t>
-        </is>
-      </c>
-      <c r="J20" s="61" t="n"/>
-      <c r="K20" s="151" t="inlineStr">
-        <is>
-          <t>ما زالت بعض الصفحات الداخلية تستخدم خط الأيقونات القديم (Font Awesome)؛ استبدالها الكامل بمكتبة أيقونات كود المنصات مجدول في المرحلة التالية.</t>
-        </is>
-      </c>
+          <t>مكتبة أيقونات موحدة: جميع الأيقونات خطية SVG (stroke 2px) بأحجام 16/20/24px وبألوان محايدة، وألوان الحالات للتنبيهات فقط، والأيقونات الكبيرة بصيغة Featured icon (48px بخلفية خفيفة). طبقة dga-icons.js تستبدل أي أيقونة قديمة (Font Awesome) تلقائياً بأيقونة المكتبة الموحدة دون تغيير الحجم أو اللون.</t>
+        </is>
+      </c>
+      <c r="J20" s="156" t="inlineStr">
+        <is>
+          <t>docs/dga/screenshots/course-service-page.png</t>
+        </is>
+      </c>
+      <c r="K20" s="89" t="n"/>
     </row>
     <row r="21" ht="50.1" customHeight="1" s="95">
       <c r="C21" s="19" t="n"/>
@@ -1827,13 +1831,13 @@
       <c r="F21" s="131" t="n"/>
       <c r="G21" s="133" t="inlineStr">
         <is>
-          <t>تطبيق جزئي</t>
+          <t>تطبيق كلي</t>
         </is>
       </c>
       <c r="H21" s="131" t="n"/>
       <c r="I21" s="152" t="inlineStr">
         <is>
-          <t>الأيقونات الجديدة SVG خطية موحدة الحجم واللون؛ الصفحات القديمة ما زالت تستخدم Font Awesome.</t>
+          <t>مكتبة أيقونات واحدة (SVG خطية) في كل الصفحات؛ لم يتبقَّ أي استخدام لخط الأيقونات القديم في واجهات الزائر (تم التحقق آلياً: 0 عنصر Font Awesome بعد التحميل).</t>
         </is>
       </c>
       <c r="J21" s="94" t="n"/>
@@ -2118,21 +2122,25 @@
       <c r="F31" s="149" t="n"/>
       <c r="G31" s="133" t="inlineStr">
         <is>
-          <t>تطبيق جزئي</t>
-        </is>
-      </c>
-      <c r="H31" s="45" t="n"/>
+          <t>تطبيق كلي</t>
+        </is>
+      </c>
+      <c r="H31" s="150" t="inlineStr">
+        <is>
+          <t>app/Application/views/website/courses/page.blade.php</t>
+        </is>
+      </c>
       <c r="I31" s="152" t="inlineStr">
         <is>
-          <t>صفحة الدورة تحتوي على بطاقة تفاصيل الخدمة (السعر/المدة/المحاضرات) وزر إجرائي وتقييم وتغذية راجعة.</t>
-        </is>
-      </c>
-      <c r="J31" s="61" t="n"/>
-      <c r="K31" s="151" t="inlineStr">
-        <is>
-          <t>توحيد مسميات الأقسام (الخطوات، الشروط، المستندات المطلوبة، بطاقة تفاصيل الخدمة) في صفحة الدورة مجدول في المرحلة التالية.</t>
-        </is>
-      </c>
+          <t>صفحة الدورة (الخدمة) مبنية على قالب صفحة الخدمة: مسار تصفح، بطاقة تفاصيل الخدمة، وصف الخدمة، الخطوات، الشروط، المستندات المطلوبة، المحتوى، المدرب، التقييم والتغذية الراجعة، مع زر إجرائي ثابت.</t>
+        </is>
+      </c>
+      <c r="J31" s="156" t="inlineStr">
+        <is>
+          <t>docs/dga/screenshots/course-service-page.png</t>
+        </is>
+      </c>
+      <c r="K31" s="89" t="n"/>
     </row>
     <row r="32" ht="93" customHeight="1" s="95">
       <c r="C32" s="19" t="n"/>
@@ -2149,13 +2157,13 @@
       <c r="F32" s="131" t="n"/>
       <c r="G32" s="133" t="inlineStr">
         <is>
-          <t>تطبيق جزئي</t>
+          <t>تطبيق كلي</t>
         </is>
       </c>
       <c r="H32" s="131" t="n"/>
       <c r="I32" s="151" t="inlineStr">
         <is>
-          <t>المصطلحات الحالية: "محتوى الدورة"، "عن المدرب"، "التقييمات"؛ يجري توحيدها مع قالب صفحة الخدمة.</t>
+          <t>العناوين والمصطلحات مطابقة للقالب: "بطاقة تفاصيل الخدمة" (اسم الخدمة، التصنيف، المدة، عدد المحاضرات، اللغة، الرسوم، الشهادة، قناة التقديم، المستفيدون)، "وصف الخدمة"، "الخطوات" (4 خطوات بمكون Steps)، "الشروط"، "المستندات المطلوبة".</t>
         </is>
       </c>
       <c r="J32" s="94" t="n"/>
@@ -5359,23 +5367,22 @@
       </c>
       <c r="G146" s="133" t="inlineStr">
         <is>
-          <t>تطبيق جزئي</t>
+          <t>تطبيق كلي</t>
         </is>
       </c>
       <c r="H146" s="150" t="inlineStr">
         <is>
-          <t>public/website/css/front/dga-platforms-code.css §6</t>
+          <t>public/website/js/dga-datepicker.js + public/website/css/front/dga-platforms-code.css §27</t>
         </is>
       </c>
       <c r="I146" s="152" t="inlineStr">
         <is>
-          <t>حقول التاريخ بنمط حقل الإدخال وحالاته.</t>
-        </is>
-      </c>
-      <c r="J146" s="66" t="n"/>
-      <c r="K146" s="152" t="inlineStr">
-        <is>
-          <t>التقويم المنسدل يعتمد على المتصفح؛ مكون التقويم المعتمد (Selected/Today/Next-Prev) مجدول في المرحلة التالية.</t>
+          <t>مكون محدد التاريخ وفق كود المنصات: حقل إدخال بزر تقويم، ونافذة تقويم منبثقة بشبكة الأيام وأزرار الشهر السابق/التالي وأزرار اليوم/مسح، مع دعم لوحة المفاتيح وقارئ الشاشة.</t>
+        </is>
+      </c>
+      <c r="J146" s="163" t="inlineStr">
+        <is>
+          <t>docs/dga/screenshots/datepicker.png</t>
         </is>
       </c>
     </row>
@@ -5446,13 +5453,13 @@
       <c r="F149" s="131" t="n"/>
       <c r="G149" s="52" t="inlineStr">
         <is>
-          <t>تطبيق جزئي</t>
+          <t>تطبيق كلي</t>
         </is>
       </c>
       <c r="H149" s="56" t="n"/>
       <c r="I149" s="154" t="inlineStr">
         <is>
-          <t>حالات التقويم (Selected/Today/Next-Prev) بتصميم المتصفح الافتراضي حالياً.</t>
+          <t>Selected (خلفية أساسية ونص أبيض)، Today (إطار أساسي)، Next/Prev (أزرار 36px بحدود)، والأيام خارج النطاق Disabled.</t>
         </is>
       </c>
       <c r="J149" s="84" t="n"/>

--- a/docs/dga/نموذج الالتزام - منصة الشهادات الاحترافية - جامعة شقراء.xlsx
+++ b/docs/dga/نموذج الالتزام - منصة الشهادات الاحترافية - جامعة شقراء.xlsx
@@ -672,6 +672,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -683,9 +686,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="I6" s="148" t="inlineStr">
         <is>
-          <t>تم تطبيق أساسات كود المنصات v1.0 (رموز الألوان، الخطوط، المسافات، الحواف، الظلال، حلقة التركيز) في ملف موحّد يُحمَّل في جميع صفحات المنصة بعد الأنماط القديمة ليحكم شكل كل المكونات.</t>
+          <t>تم تطبيق أساسات كود المنصات v1.0 (رموز الألوان، الخطوط، المسافات، الحواف، الظلال، حلقة التركيز) في ملف موحّد يُحمَّل في جميع صفحات المنصة، مع مطابقة القيم والمكونات لما هو مطبق في موقع جامعة شقراء المعتمد من الهيئة (su.edu.sa).</t>
         </is>
       </c>
       <c r="J6" s="148" t="inlineStr">
@@ -1400,15 +1400,19 @@
       </c>
       <c r="H7" s="150" t="inlineStr">
         <is>
-          <t>public/website/css/front/dga-platforms-code.css §1</t>
+          <t>public/website/css/front/dga-platforms-code.css §1 / §29</t>
         </is>
       </c>
       <c r="I7" s="151" t="inlineStr">
         <is>
-          <t>لوحة الألوان المحايدة (Gray 25–950) وألوان الحالات (Error/Warning/Success/Info) بقيم كود المنصات نفسها؛ اللون الأساسي بهوية الجهة (أخضر جامعة شقراء) على مقياس 25–950.</t>
-        </is>
-      </c>
-      <c r="J7" s="60" t="n"/>
+          <t>الألوان مطابقة لكود المنصات ولموقع جامعة شقراء المعتمد (su.edu.sa): اللون الأساسي Primary-600 #1B8354 (hover 700 #166A45، pressed 900)، المحايد Gray 25–950، ألوان الحالات Error/Warning/Success/Info، لون النص الافتراضي #161616، وخلفية التذييل Success-900 #074D31.</t>
+        </is>
+      </c>
+      <c r="J7" s="152" t="inlineStr">
+        <is>
+          <t>docs/dga/screenshots/reference-su-edu-sa.png</t>
+        </is>
+      </c>
       <c r="K7" s="13" t="n"/>
     </row>
     <row r="8" ht="51" customHeight="1" s="95">
@@ -1434,7 +1438,7 @@
           <t>public/website/css/front/dga-platforms-code.css §1</t>
         </is>
       </c>
-      <c r="I8" s="152" t="inlineStr">
+      <c r="I8" s="153" t="inlineStr">
         <is>
           <t>جميع المكونات تستخدم رموز الألوان --dga-color-* (background / text / border / form-field) دون قيم مباشرة، وتم ربط الأسماء القديمة بالرموز الجديدة.</t>
         </is>
@@ -1470,7 +1474,7 @@
           <t>العناصر على الخلفيات الملونة تستخدم متغيرات On-Color (أزرار on-color، نص أبيض على الأخضر الداكن بتباين ≥ 4.5:1، نص داكن على الذهبي).</t>
         </is>
       </c>
-      <c r="J9" s="153" t="n"/>
+      <c r="J9" s="154" t="n"/>
       <c r="K9" s="143" t="n"/>
     </row>
     <row r="10" ht="45" customHeight="1" s="95">
@@ -1512,7 +1516,7 @@
           <t>public/website/css/front/dga-platforms-code.css §2</t>
         </is>
       </c>
-      <c r="I11" s="152" t="inlineStr">
+      <c r="I11" s="153" t="inlineStr">
         <is>
           <t>الخط المعتمد IBM Plex Sans Arabic مع رموز Display/Text وأوزان العناوين 600 والنص 400 ومقاس متجاوب.</t>
         </is>
@@ -1543,7 +1547,7 @@
           <t>public/website/css/front/dga-platforms-code.css §2</t>
         </is>
       </c>
-      <c r="I12" s="152" t="inlineStr">
+      <c r="I12" s="153" t="inlineStr">
         <is>
           <t>IBM Plex Sans Arabic محمَّل من Google Fonts (preconnect) ومعرَّف كخط افتراضي للجسم والعناوين والنماذج والأزرار.</t>
         </is>
@@ -1573,12 +1577,12 @@
           <t>تطبيق كلي</t>
         </is>
       </c>
-      <c r="H13" s="154" t="inlineStr">
+      <c r="H13" s="155" t="inlineStr">
         <is>
           <t>public/website/css/front/dga-platforms-code.css §2</t>
         </is>
       </c>
-      <c r="I13" s="154" t="inlineStr">
+      <c r="I13" s="155" t="inlineStr">
         <is>
           <t>رموز Display (xs–xl) وText (xs–xl) مع line-height لكل مقاس، وتصغير تلقائي للعناوين على الشاشات الأصغر من 992px.</t>
         </is>
@@ -1613,7 +1617,7 @@
           <t>public/website/css/front/dga-platforms-code.css §1 / §24</t>
         </is>
       </c>
-      <c r="I14" s="152" t="inlineStr">
+      <c r="I14" s="153" t="inlineStr">
         <is>
           <t>المسافات بين العناصر والأقسام من مقياس 4px (2/4/6/8/12/16/20/24/32/40/48/64).</t>
         </is>
@@ -1644,7 +1648,7 @@
           <t>public/website/css/front/dga-platforms-code.css</t>
         </is>
       </c>
-      <c r="I15" s="152" t="inlineStr">
+      <c r="I15" s="153" t="inlineStr">
         <is>
           <t>وحدات القياس المعتمدة مطبقة على الأزرار (40/48px)، الحقول (40px)، البطاقات (24px)، الأقسام (64px).</t>
         </is>
@@ -1670,12 +1674,12 @@
           <t>تطبيق كلي</t>
         </is>
       </c>
-      <c r="H16" s="154" t="inlineStr">
+      <c r="H16" s="155" t="inlineStr">
         <is>
           <t>public/website/css/front/dga-platforms-code.css</t>
         </is>
       </c>
-      <c r="I16" s="154" t="inlineStr">
+      <c r="I16" s="155" t="inlineStr">
         <is>
           <t>استخدام رموز المسافات العامة --dga-space-* فقط في المكونات الجديدة والقوالب.</t>
         </is>
@@ -1684,7 +1688,7 @@
       <c r="K16" s="54" t="n"/>
     </row>
     <row r="17" ht="72" customHeight="1" s="95">
-      <c r="B17" s="155">
+      <c r="B17" s="156">
         <f>MAX($B$5:B16)+1</f>
         <v/>
       </c>
@@ -1706,12 +1710,12 @@
         </is>
       </c>
       <c r="H17" s="45" t="n"/>
-      <c r="I17" s="152" t="inlineStr">
+      <c r="I17" s="153" t="inlineStr">
         <is>
           <t>الشبكات تعيد الترتيب تلقائياً (Grid auto-fit) للجوال/اللوحي/سطح المكتب، وشريط تنقل منزلق للجوال.</t>
         </is>
       </c>
-      <c r="J17" s="156" t="inlineStr">
+      <c r="J17" s="152" t="inlineStr">
         <is>
           <t>docs/dga/screenshots/home.png</t>
         </is>
@@ -1778,7 +1782,7 @@
       <c r="K19" s="24" t="n"/>
     </row>
     <row r="20" ht="50.1" customHeight="1" s="95">
-      <c r="B20" s="155">
+      <c r="B20" s="156">
         <f>MAX($B$5:B19)+1</f>
         <v/>
       </c>
@@ -1804,12 +1808,12 @@
           <t>public/website/js/dga-icons.js</t>
         </is>
       </c>
-      <c r="I20" s="152" t="inlineStr">
+      <c r="I20" s="153" t="inlineStr">
         <is>
           <t>مكتبة أيقونات موحدة: جميع الأيقونات خطية SVG (stroke 2px) بأحجام 16/20/24px وبألوان محايدة، وألوان الحالات للتنبيهات فقط، والأيقونات الكبيرة بصيغة Featured icon (48px بخلفية خفيفة). طبقة dga-icons.js تستبدل أي أيقونة قديمة (Font Awesome) تلقائياً بأيقونة المكتبة الموحدة دون تغيير الحجم أو اللون.</t>
         </is>
       </c>
-      <c r="J20" s="156" t="inlineStr">
+      <c r="J20" s="152" t="inlineStr">
         <is>
           <t>docs/dga/screenshots/course-service-page.png</t>
         </is>
@@ -1835,7 +1839,7 @@
         </is>
       </c>
       <c r="H21" s="131" t="n"/>
-      <c r="I21" s="152" t="inlineStr">
+      <c r="I21" s="153" t="inlineStr">
         <is>
           <t>مكتبة أيقونات واحدة (SVG خطية) في كل الصفحات؛ لم يتبقَّ أي استخدام لخط الأيقونات القديم في واجهات الزائر (تم التحقق آلياً: 0 عنصر Font Awesome بعد التحميل).</t>
         </is>
@@ -1870,7 +1874,7 @@
         </is>
       </c>
       <c r="H22" s="131" t="n"/>
-      <c r="I22" s="152" t="inlineStr">
+      <c r="I22" s="153" t="inlineStr">
         <is>
           <t>ألوان الحالات (نجاح/فشل/تحذير/معلومة) تُستخدم فقط في التنبيهات والعلامات التنبيهية، وباقي الأيقونات رمادية/أساسية.</t>
         </is>
@@ -1897,7 +1901,7 @@
         </is>
       </c>
       <c r="H23" s="131" t="n"/>
-      <c r="I23" s="152" t="inlineStr">
+      <c r="I23" s="153" t="inlineStr">
         <is>
           <t>الأيقونات الأكبر من 24px ضمن Featured icon (حاوية 48px بخلفية primary-50) في بطاقات الخدمات والمزايا.</t>
         </is>
@@ -1952,12 +1956,12 @@
         </is>
       </c>
       <c r="H25" s="45" t="n"/>
-      <c r="I25" s="152" t="inlineStr">
+      <c r="I25" s="153" t="inlineStr">
         <is>
           <t>قالب الصفحة الرئيسية: الختم الرقمي ← شريط التنقل ← القسم الرئيسي ← الخدمات ← من نحن ← التصنيفات ← الدورات ← الشركاء ← التذييل.</t>
         </is>
       </c>
-      <c r="J25" s="156" t="inlineStr">
+      <c r="J25" s="152" t="inlineStr">
         <is>
           <t>docs/dga/screenshots/home.png</t>
         </is>
@@ -1983,7 +1987,7 @@
         </is>
       </c>
       <c r="H26" s="131" t="n"/>
-      <c r="I26" s="152" t="inlineStr">
+      <c r="I26" s="153" t="inlineStr">
         <is>
           <t>القسم الرئيسي من نوع "صورة" مع طبقة لونية وحقل بحث وزرين إجرائيين (primary + on-color).</t>
         </is>
@@ -2036,12 +2040,12 @@
           <t>app/Application/views/website/professionalcertificates.blade.php</t>
         </is>
       </c>
-      <c r="I28" s="152" t="inlineStr">
+      <c r="I28" s="153" t="inlineStr">
         <is>
           <t>تمت إضافة قسم "خدمات المنصة" مباشرة بعد القسم الرئيسي (6 بطاقات خدمة بأيقونة + عنوان + وصف + زر "ابدأ الخدمة").</t>
         </is>
       </c>
-      <c r="J28" s="156" t="inlineStr">
+      <c r="J28" s="152" t="inlineStr">
         <is>
           <t>docs/dga/screenshots/home.png</t>
         </is>
@@ -2130,12 +2134,12 @@
           <t>app/Application/views/website/courses/page.blade.php</t>
         </is>
       </c>
-      <c r="I31" s="152" t="inlineStr">
+      <c r="I31" s="153" t="inlineStr">
         <is>
           <t>صفحة الدورة (الخدمة) مبنية على قالب صفحة الخدمة: مسار تصفح، بطاقة تفاصيل الخدمة، وصف الخدمة، الخطوات، الشروط، المستندات المطلوبة، المحتوى، المدرب، التقييم والتغذية الراجعة، مع زر إجرائي ثابت.</t>
         </is>
       </c>
-      <c r="J31" s="156" t="inlineStr">
+      <c r="J31" s="152" t="inlineStr">
         <is>
           <t>docs/dga/screenshots/course-service-page.png</t>
         </is>
@@ -2188,7 +2192,7 @@
         </is>
       </c>
       <c r="H33" s="45" t="n"/>
-      <c r="I33" s="152" t="inlineStr">
+      <c r="I33" s="153" t="inlineStr">
         <is>
           <t>مكون التقييم بالنجوم (Selected/Half) مطبق في صفحة الدورة.</t>
         </is>
@@ -2247,7 +2251,7 @@
         </is>
       </c>
       <c r="H35" s="45" t="n"/>
-      <c r="I35" s="152" t="inlineStr">
+      <c r="I35" s="153" t="inlineStr">
         <is>
           <t>منصة خدمية تعليمية تابعة لجامعة شقراء، وقالب المشاركة الإلكترونية متاح على الموقع الرئيسي للجامعة su.edu.sa، ولا تقدم المنصة استشارات عامة أو استطلاعات تشريعية.</t>
         </is>
@@ -2274,7 +2278,7 @@
         </is>
       </c>
       <c r="H36" s="45" t="n"/>
-      <c r="I36" s="152" t="inlineStr">
+      <c r="I36" s="153" t="inlineStr">
         <is>
           <t>منصة خدمية تعليمية تابعة لجامعة شقراء، وقالب المشاركة الإلكترونية متاح على الموقع الرئيسي للجامعة su.edu.sa، ولا تقدم المنصة استشارات عامة أو استطلاعات تشريعية.</t>
         </is>
@@ -2301,7 +2305,7 @@
         </is>
       </c>
       <c r="H37" s="53" t="n"/>
-      <c r="I37" s="154" t="inlineStr">
+      <c r="I37" s="155" t="inlineStr">
         <is>
           <t>منصة خدمية تعليمية تابعة لجامعة شقراء، وقالب المشاركة الإلكترونية متاح على الموقع الرئيسي للجامعة su.edu.sa، ولا تقدم المنصة استشارات عامة أو استطلاعات تشريعية.</t>
         </is>
@@ -2332,12 +2336,12 @@
         </is>
       </c>
       <c r="H38" s="45" t="n"/>
-      <c r="I38" s="152" t="inlineStr">
+      <c r="I38" s="153" t="inlineStr">
         <is>
           <t>قالب البحث: حقل بحث كود المنصات (أيقونة + زر) في الهيدر والقسم الرئيسي وأعلى صفحة النتائج، مع فلترة جانبية وتبويبات.</t>
         </is>
       </c>
-      <c r="J38" s="156" t="inlineStr">
+      <c r="J38" s="152" t="inlineStr">
         <is>
           <t>docs/dga/screenshots/search-results.png</t>
         </is>
@@ -2363,7 +2367,7 @@
         </is>
       </c>
       <c r="H39" s="131" t="n"/>
-      <c r="I39" s="152" t="inlineStr">
+      <c r="I39" s="153" t="inlineStr">
         <is>
           <t>حقل البحث بارتفاع 48px وحواف 4px وأيقونة بحث وزر أساسي، وصفحة نتائج بتبويبات وفلاتر.</t>
         </is>
@@ -2394,7 +2398,7 @@
           <t>app/Application/views/website/courses/assets/coursesPerCategory.blade.php</t>
         </is>
       </c>
-      <c r="I40" s="152" t="inlineStr">
+      <c r="I40" s="153" t="inlineStr">
         <is>
           <t>شريط البحث متاح أعلى صفحة النتائج مع كلمة البحث الحالية.</t>
         </is>
@@ -2490,10 +2494,10 @@
       </c>
       <c r="I43" s="151" t="inlineStr">
         <is>
-          <t>الختم الرقمي أعلى كل صفحة: شعار المملكة + "موقع رسمي تابع لحكومة المملكة العربية السعودية" + "كيف تتحقق؟" قابل للتوسيع.</t>
-        </is>
-      </c>
-      <c r="J43" s="156" t="inlineStr">
+          <t>الختم الرقمي أعلى كل صفحة بنفس نمط موقع الجامعة المعتمد: شعار المملكة + "موقع حكومي مسجل لدى هيئة الحكومة الرقمية" + "كيف تتحقق؟" قابل للتوسيع، يليه شريط الأدوات (التاريخ، الوقت، المدينة، وأدوات الوصول).</t>
+        </is>
+      </c>
+      <c r="J43" s="152" t="inlineStr">
         <is>
           <t>docs/dga/screenshots/home.png</t>
         </is>
@@ -2519,7 +2523,7 @@
         </is>
       </c>
       <c r="H44" s="131" t="n"/>
-      <c r="I44" s="152" t="inlineStr">
+      <c r="I44" s="153" t="inlineStr">
         <is>
           <t>الختم أول عنصر في الصفحة قبل شريط التنقل.</t>
         </is>
@@ -2546,7 +2550,7 @@
         </is>
       </c>
       <c r="H45" s="131" t="n"/>
-      <c r="I45" s="152" t="inlineStr">
+      <c r="I45" s="153" t="inlineStr">
         <is>
           <t>تفاصيل التحقق تربط بسجل المنصات الحكومية لدى هيئة الحكومة الرقمية وتوضح النطاقات الرسمية (edu.sa / gov.sa) و HTTPS.</t>
         </is>
@@ -2574,9 +2578,9 @@
         </is>
       </c>
       <c r="H46" s="55" t="n"/>
-      <c r="I46" s="154" t="inlineStr">
-        <is>
-          <t>عنصران ثانويان فقط على الجانب المقابل: مبدّل اللغة وأدوات إمكانية الوصول.</t>
+      <c r="I46" s="155" t="inlineStr">
+        <is>
+          <t>لا توجد عناصر ثانوية داخل الختم؛ أدوات الوصول في شريط الأدوات أسفله ومبدّل اللغة في شريط التنقل (كما في su.edu.sa).</t>
         </is>
       </c>
       <c r="J46" s="62" t="n"/>
@@ -2609,7 +2613,7 @@
           <t>public/website/css/front/dga-platforms-code.css §5</t>
         </is>
       </c>
-      <c r="I47" s="152" t="inlineStr">
+      <c r="I47" s="153" t="inlineStr">
         <is>
           <t>مكون الزر بكامل أنواعه وحالاته.</t>
         </is>
@@ -2636,7 +2640,7 @@
         </is>
       </c>
       <c r="H48" s="131" t="n"/>
-      <c r="I48" s="152" t="inlineStr">
+      <c r="I48" s="153" t="inlineStr">
         <is>
           <t>ارتفاع 40px (و48px للكبير)، حواف 4px، خط 16px وزن 500، أنواع primary / secondary / outline / neutral / ghost / danger / on-color، ويُطبق على الأزرار القديمة أيضاً.</t>
         </is>
@@ -2663,7 +2667,7 @@
         </is>
       </c>
       <c r="H49" s="53" t="n"/>
-      <c r="I49" s="154" t="inlineStr">
+      <c r="I49" s="155" t="inlineStr">
         <is>
           <t>الحالات: Default، Hover (درجة أغمق)، Pressed (800)، Selected، Focus (إطار أسود 2px بإزاحة 2px)، Disabled (رمادي 100 / نص رمادي 400)، Loading.</t>
         </is>
@@ -2725,7 +2729,7 @@
         </is>
       </c>
       <c r="H51" s="131" t="n"/>
-      <c r="I51" s="152" t="inlineStr">
+      <c r="I51" s="153" t="inlineStr">
         <is>
           <t>حدود 1px رمادي 400، حواف 4px، ارتفاع 40px، أيقونة سهم، عناصر القائمة 40px بحواف 4px وظل md.</t>
         </is>
@@ -2815,7 +2819,7 @@
         </is>
       </c>
       <c r="H54" s="131" t="n"/>
-      <c r="I54" s="152" t="inlineStr">
+      <c r="I54" s="153" t="inlineStr">
         <is>
           <t>الروابط النصية باللون الأساسي مع تسطير وإزاحة 0.2em، وروابط التنقل بدون تسطير.</t>
         </is>
@@ -2842,7 +2846,7 @@
         </is>
       </c>
       <c r="H55" s="131" t="n"/>
-      <c r="I55" s="152" t="inlineStr">
+      <c r="I55" s="153" t="inlineStr">
         <is>
           <t>الحالات: Default، Hover (700)، Pressed (800)، Focus (إطار أسود)، Visited (800)، Disabled (رمادي 400 وغير قابل للنقر).</t>
         </is>
@@ -2909,12 +2913,12 @@
           <t>public/website/css/front/dga-platforms-code.css §12</t>
         </is>
       </c>
-      <c r="I57" s="152" t="inlineStr">
+      <c r="I57" s="153" t="inlineStr">
         <is>
           <t>الأكورديون (الأسئلة الشائعة) وفق كود المنصات.</t>
         </is>
       </c>
-      <c r="J57" s="156" t="inlineStr">
+      <c r="J57" s="152" t="inlineStr">
         <is>
           <t>docs/dga/screenshots/faq-accordion.png</t>
         </is>
@@ -2940,7 +2944,7 @@
         </is>
       </c>
       <c r="H58" s="131" t="n"/>
-      <c r="I58" s="152" t="inlineStr">
+      <c r="I58" s="153" t="inlineStr">
         <is>
           <t>عناصر بفواصل 1px، رأس 56px، عنوان 16px وزن 500، سهم 20px.</t>
         </is>
@@ -3030,7 +3034,7 @@
           <t>public/website/css/front/dga-platforms-code.css §22</t>
         </is>
       </c>
-      <c r="I61" s="152" t="inlineStr">
+      <c r="I61" s="153" t="inlineStr">
         <is>
           <t>قائمة التنقل وقوائمها الفرعية وفق كود المنصات.</t>
         </is>
@@ -3057,7 +3061,7 @@
         </is>
       </c>
       <c r="H62" s="45" t="n"/>
-      <c r="I62" s="152" t="inlineStr">
+      <c r="I62" s="153" t="inlineStr">
         <is>
           <t>روابط 44px بحواف 4px، قائمة منسدلة بحدود وظل، عناصر 40px.</t>
         </is>
@@ -3084,7 +3088,7 @@
         </is>
       </c>
       <c r="H63" s="45" t="n"/>
-      <c r="I63" s="152" t="inlineStr">
+      <c r="I63" s="153" t="inlineStr">
         <is>
           <t>الحالات: Hover (خلفية 50)، Pressed (100)، Focus (إطار أسود)، Disabled.</t>
         </is>
@@ -3241,7 +3245,7 @@
           <t>public/website/css/front/dga-platforms-code.css §13</t>
         </is>
       </c>
-      <c r="I69" s="152" t="inlineStr">
+      <c r="I69" s="153" t="inlineStr">
         <is>
           <t>الإشعارات بأنواعها الأربعة.</t>
         </is>
@@ -3268,7 +3272,7 @@
         </is>
       </c>
       <c r="H70" s="35" t="n"/>
-      <c r="I70" s="152" t="inlineStr">
+      <c r="I70" s="153" t="inlineStr">
         <is>
           <t>Inline Alert: حدود 1px بلون الحالة 300، خلفية 50، أيقونة 20px بلون 600، حواف 4px، زر إغلاق 32px؛ ويُطبق على تنبيهات Bootstrap الحالية.</t>
         </is>
@@ -3294,7 +3298,7 @@
         </is>
       </c>
       <c r="H71" s="35" t="n"/>
-      <c r="I71" s="152" t="inlineStr">
+      <c r="I71" s="153" t="inlineStr">
         <is>
           <t>الإشعارات المؤقتة (نجاح الإرسال، إضافة للسلة) تظهر كـ Toast في زاوية الشاشة.</t>
         </is>
@@ -3321,7 +3325,7 @@
         </is>
       </c>
       <c r="H72" s="35" t="n"/>
-      <c r="I72" s="152" t="inlineStr">
+      <c r="I72" s="153" t="inlineStr">
         <is>
           <t>الإشعارات الدائمة (أخطاء النماذج، معلومات الاشتراك) Inline Alert ضمن السياق.</t>
         </is>
@@ -3347,7 +3351,7 @@
         </is>
       </c>
       <c r="H73" s="35" t="n"/>
-      <c r="I73" s="152" t="inlineStr">
+      <c r="I73" s="153" t="inlineStr">
         <is>
           <t>الإشعارات عالية الأولوية أعلى الصفحة بنمط Notification (عرض كامل بدون حواف).</t>
         </is>
@@ -3373,7 +3377,7 @@
         </is>
       </c>
       <c r="H74" s="35" t="n"/>
-      <c r="I74" s="152" t="inlineStr">
+      <c r="I74" s="153" t="inlineStr">
         <is>
           <t>النجاح أخضر، الخطأ أحمر، التحذير برتقالي، المعلومة أزرق حسب السياق.</t>
         </is>
@@ -3461,7 +3465,7 @@
         </is>
       </c>
       <c r="H77" s="35" t="n"/>
-      <c r="I77" s="152" t="inlineStr">
+      <c r="I77" s="153" t="inlineStr">
         <is>
           <t>حواف 8px، حدود 1px، ظل xl، خلفية معتمة 50%، زر إغلاق 40px، عناوين 18px وزن 600.</t>
         </is>
@@ -3655,7 +3659,7 @@
           <t>public/website/css/front/dga-platforms-code.css §7</t>
         </is>
       </c>
-      <c r="I85" s="152" t="inlineStr">
+      <c r="I85" s="153" t="inlineStr">
         <is>
           <t>مربع الاختيار المخصص 20px.</t>
         </is>
@@ -3681,7 +3685,7 @@
         </is>
       </c>
       <c r="H86" s="35" t="n"/>
-      <c r="I86" s="152" t="inlineStr">
+      <c r="I86" s="153" t="inlineStr">
         <is>
           <t>20px، حواف 4px، حد رمادي 400، تعبئة باللون الأساسي عند التحديد مع علامة صح بيضاء.</t>
         </is>
@@ -3706,7 +3710,7 @@
         </is>
       </c>
       <c r="H87" s="35" t="n"/>
-      <c r="I87" s="152" t="inlineStr">
+      <c r="I87" s="153" t="inlineStr">
         <is>
           <t>Hover (حد أساسي)، Focus (إطار أسود)، Read-only، Disabled (رمادي).</t>
         </is>
@@ -3767,7 +3771,7 @@
           <t>public/website/css/front/dga-platforms-code.css §7</t>
         </is>
       </c>
-      <c r="I89" s="152" t="inlineStr">
+      <c r="I89" s="153" t="inlineStr">
         <is>
           <t>زر الاختيار المخصص 20px دائري.</t>
         </is>
@@ -3793,7 +3797,7 @@
         </is>
       </c>
       <c r="H90" s="35" t="n"/>
-      <c r="I90" s="152" t="inlineStr">
+      <c r="I90" s="153" t="inlineStr">
         <is>
           <t>20px دائري، حد رمادي 400، نقطة بيضاء 8px عند التحديد.</t>
         </is>
@@ -3819,7 +3823,7 @@
         </is>
       </c>
       <c r="H91" s="35" t="n"/>
-      <c r="I91" s="152" t="inlineStr">
+      <c r="I91" s="153" t="inlineStr">
         <is>
           <t>Hover، Focus، Read-only، Disabled.</t>
         </is>
@@ -3845,7 +3849,7 @@
         </is>
       </c>
       <c r="H92" s="56" t="n"/>
-      <c r="I92" s="154" t="inlineStr">
+      <c r="I92" s="155" t="inlineStr">
         <is>
           <t>Selected / Unselected.</t>
         </is>
@@ -3876,7 +3880,7 @@
         </is>
       </c>
       <c r="H93" s="45" t="n"/>
-      <c r="I93" s="152" t="inlineStr">
+      <c r="I93" s="153" t="inlineStr">
         <is>
           <t>لا يوجد زر تبديل في واجهات الزائر؛ المكون (.dga-switch) جاهز في ملف الأنماط لاستخدامه مستقبلاً بحالاته On/Off/Hover/Focus/Disabled.</t>
         </is>
@@ -3902,7 +3906,7 @@
         </is>
       </c>
       <c r="H94" s="35" t="n"/>
-      <c r="I94" s="152" t="inlineStr">
+      <c r="I94" s="153" t="inlineStr">
         <is>
           <t>لا يوجد زر تبديل في واجهات الزائر؛ المكون (.dga-switch) جاهز في ملف الأنماط لاستخدامه مستقبلاً بحالاته On/Off/Hover/Focus/Disabled.</t>
         </is>
@@ -3928,7 +3932,7 @@
         </is>
       </c>
       <c r="H95" s="35" t="n"/>
-      <c r="I95" s="152" t="inlineStr">
+      <c r="I95" s="153" t="inlineStr">
         <is>
           <t>لا يوجد زر تبديل في واجهات الزائر؛ المكون (.dga-switch) جاهز في ملف الأنماط لاستخدامه مستقبلاً بحالاته On/Off/Hover/Focus/Disabled.</t>
         </is>
@@ -3989,7 +3993,7 @@
           <t>public/website/css/front/dga-platforms-code.css §6</t>
         </is>
       </c>
-      <c r="I97" s="152" t="inlineStr">
+      <c r="I97" s="153" t="inlineStr">
         <is>
           <t>منطقة النص وفق كود المنصات.</t>
         </is>
@@ -4015,7 +4019,7 @@
         </is>
       </c>
       <c r="H98" s="35" t="n"/>
-      <c r="I98" s="152" t="inlineStr">
+      <c r="I98" s="153" t="inlineStr">
         <is>
           <t>نفس حقل الإدخال: حد رمادي 400، حواف 4px، ارتفاع أدنى 120px، تغيير الحجم رأسياً.</t>
         </is>
@@ -4041,7 +4045,7 @@
         </is>
       </c>
       <c r="H99" s="35" t="n"/>
-      <c r="I99" s="152" t="inlineStr">
+      <c r="I99" s="153" t="inlineStr">
         <is>
           <t>Default، Hover، Pressed/Focus، Read-only، Disabled.</t>
         </is>
@@ -4067,7 +4071,7 @@
         </is>
       </c>
       <c r="H100" s="56" t="n"/>
-      <c r="I100" s="154" t="inlineStr">
+      <c r="I100" s="155" t="inlineStr">
         <is>
           <t>Placeholder رمادي 500، نص مساعد 14px رمادي 700، رسالة خطأ بأيقونة وبلون أحمر 700.</t>
         </is>
@@ -4102,7 +4106,7 @@
           <t>public/website/css/front/dga-platforms-code.css §11</t>
         </is>
       </c>
-      <c r="I101" s="152" t="inlineStr">
+      <c r="I101" s="153" t="inlineStr">
         <is>
           <t>التبويبات بنمط الخط السفلي وفق كود المنصات.</t>
         </is>
@@ -4158,7 +4162,7 @@
         </is>
       </c>
       <c r="H103" s="35" t="n"/>
-      <c r="I103" s="152" t="inlineStr">
+      <c r="I103" s="153" t="inlineStr">
         <is>
           <t>Hover (خلفية رمادية 50 ونص 900)، Focus (إطار أسود)، Disabled (رمادي 400).</t>
         </is>
@@ -4210,7 +4214,7 @@
         </is>
       </c>
       <c r="H105" s="56" t="n"/>
-      <c r="I105" s="154" t="inlineStr">
+      <c r="I105" s="155" t="inlineStr">
         <is>
           <t>نص موحد الخط والحجم والمحاذاة مع تمرير أفقي على الجوال.</t>
         </is>
@@ -4245,7 +4249,7 @@
           <t>public/website/css/front/dga-platforms-code.css §8</t>
         </is>
       </c>
-      <c r="I106" s="152" t="inlineStr">
+      <c r="I106" s="153" t="inlineStr">
         <is>
           <t>العلامات بأنواعها.</t>
         </is>
@@ -4271,7 +4275,7 @@
         </is>
       </c>
       <c r="H107" s="35" t="n"/>
-      <c r="I107" s="152" t="inlineStr">
+      <c r="I107" s="153" t="inlineStr">
         <is>
           <t>ارتفاع 24px، حواف 4px، خط 14px وزن 500، حدود 1px.</t>
         </is>
@@ -4341,7 +4345,7 @@
           <t>app/Application/views/website/theme/bootstrap/layout/footer.blade.php</t>
         </is>
       </c>
-      <c r="I109" s="152" t="inlineStr">
+      <c r="I109" s="153" t="inlineStr">
         <is>
           <t>التذييل وفق كود المنصات.</t>
         </is>
@@ -4371,7 +4375,7 @@
         </is>
       </c>
       <c r="H110" s="35" t="n"/>
-      <c r="I110" s="152" t="inlineStr">
+      <c r="I110" s="153" t="inlineStr">
         <is>
           <t>خلفية داكنة، 5 أعمدة، عناوين 16px وزن 600، روابط بحالة hover (تسطير) وأيقونة رابط خارجي.</t>
         </is>
@@ -4397,7 +4401,7 @@
         </is>
       </c>
       <c r="H111" s="35" t="n"/>
-      <c r="I111" s="152" t="inlineStr">
+      <c r="I111" s="153" t="inlineStr">
         <is>
           <t>مجموعات: عن المنصة، روابط مفيدة، الشروط والسياسات، تواصل معنا.</t>
         </is>
@@ -4424,7 +4428,7 @@
         </is>
       </c>
       <c r="H112" s="56" t="n"/>
-      <c r="I112" s="154" t="inlineStr">
+      <c r="I112" s="155" t="inlineStr">
         <is>
           <t>الروابط الرسمية (الجامعة، رؤية 2030، وزارة التعليم، المنصة الوطنية)، شعارات الجهة، بيانات التواصل، سياسة الخصوصية، بيان إمكانية الوصول، خريطة الموقع، شعار هيئة الحكومة الرقمية، آخر تحديث.</t>
         </is>
@@ -4459,7 +4463,7 @@
           <t>public/website/css/front/dga-platforms-code.css §14</t>
         </is>
       </c>
-      <c r="I113" s="152" t="inlineStr">
+      <c r="I113" s="153" t="inlineStr">
         <is>
           <t>البطاقات وفق كود المنصات.</t>
         </is>
@@ -4485,7 +4489,7 @@
         </is>
       </c>
       <c r="H114" s="35" t="n"/>
-      <c r="I114" s="152" t="inlineStr">
+      <c r="I114" s="153" t="inlineStr">
         <is>
           <t>حدود 1px رمادي 300، حواف 8px، خلفية بيضاء، حشو 24px، ظل xs للبطاقات الإجرائية.</t>
         </is>
@@ -4537,7 +4541,7 @@
         </is>
       </c>
       <c r="H116" s="35" t="n"/>
-      <c r="I116" s="152" t="inlineStr">
+      <c r="I116" s="153" t="inlineStr">
         <is>
           <t>الاختلاف بين البطاقات فقط في محاذاة العناصر الداخلية (مركزية للمزايا) والمساحات.</t>
         </is>
@@ -4563,7 +4567,7 @@
         </is>
       </c>
       <c r="H117" s="35" t="n"/>
-      <c r="I117" s="152" t="inlineStr">
+      <c r="I117" s="153" t="inlineStr">
         <is>
           <t>الأنواع: بمحتوى، بصورة (الدورات)، بظل، بدون ظل (الفلاتر).</t>
         </is>
@@ -4625,7 +4629,7 @@
           <t>public/website/css/front/dga-platforms-code.css §22</t>
         </is>
       </c>
-      <c r="I119" s="152" t="inlineStr">
+      <c r="I119" s="153" t="inlineStr">
         <is>
           <t>شريط التنقل العلوي وفق كود المنصات.</t>
         </is>
@@ -4655,7 +4659,7 @@
         </is>
       </c>
       <c r="H120" s="35" t="n"/>
-      <c r="I120" s="152" t="inlineStr">
+      <c r="I120" s="153" t="inlineStr">
         <is>
           <t>ارتفاع 72px، شعار الجهة يميناً، روابط 16px وزن 500، حقل بحث 40px، أزرار الدخول (outline) وإنشاء الحساب (primary)، شعار رؤية 2030 يساراً.</t>
         </is>
@@ -4681,7 +4685,7 @@
         </is>
       </c>
       <c r="H121" s="35" t="n"/>
-      <c r="I121" s="152" t="inlineStr">
+      <c r="I121" s="153" t="inlineStr">
         <is>
           <t>Hover، Pressed، Focus، Disabled للتبويبات والقوائم الفرعية.</t>
         </is>
@@ -4707,7 +4711,7 @@
         </is>
       </c>
       <c r="H122" s="35" t="n"/>
-      <c r="I122" s="152" t="inlineStr">
+      <c r="I122" s="153" t="inlineStr">
         <is>
           <t>Selected بخط سفلي 2px ولون أساسي مع aria-current.</t>
         </is>
@@ -4733,7 +4737,7 @@
         </is>
       </c>
       <c r="H123" s="35" t="n"/>
-      <c r="I123" s="152" t="inlineStr">
+      <c r="I123" s="153" t="inlineStr">
         <is>
           <t>قائمة منزلقة على الجوال مع أكورديون للقوائم الفرعية وشريط تنقل سفلي.</t>
         </is>
@@ -4799,7 +4803,7 @@
           <t>public/website/css/front/dga-platforms-code.css §9</t>
         </is>
       </c>
-      <c r="I125" s="152" t="inlineStr">
+      <c r="I125" s="153" t="inlineStr">
         <is>
           <t>مسار التصفح وفق كود المنصات.</t>
         </is>
@@ -4829,7 +4833,7 @@
         </is>
       </c>
       <c r="H126" s="35" t="n"/>
-      <c r="I126" s="152" t="inlineStr">
+      <c r="I126" s="153" t="inlineStr">
         <is>
           <t>خط 14px، روابط رمادي 700، فاصل سهم 16px رمادي 500، الصفحة الحالية رمادي 900 وزن 500، بدون خلفية.</t>
         </is>
@@ -4856,7 +4860,7 @@
         </is>
       </c>
       <c r="H127" s="35" t="n"/>
-      <c r="I127" s="152" t="inlineStr">
+      <c r="I127" s="153" t="inlineStr">
         <is>
           <t>الروابط: Hover (تسطير + لون أساسي)، Pressed، Focus؛ الصفحة الحالية غير قابلة للنقر مع aria-current="page" في جميع الصفحات.</t>
         </is>
@@ -4882,7 +4886,7 @@
         </is>
       </c>
       <c r="H128" s="35" t="n"/>
-      <c r="I128" s="152" t="inlineStr">
+      <c r="I128" s="153" t="inlineStr">
         <is>
           <t>يلتف على الجوال، ضمن nav بعنوان aria-label="مسار التنقل".</t>
         </is>
@@ -4944,7 +4948,7 @@
           <t>public/website/css/front/dga-platforms-code.css §20</t>
         </is>
       </c>
-      <c r="I130" s="152" t="inlineStr">
+      <c r="I130" s="153" t="inlineStr">
         <is>
           <t>الصورة الرمزية في قائمة الحساب.</t>
         </is>
@@ -4970,7 +4974,7 @@
         </is>
       </c>
       <c r="H131" s="35" t="n"/>
-      <c r="I131" s="152" t="inlineStr">
+      <c r="I131" s="153" t="inlineStr">
         <is>
           <t>40px دائرية، حد 1px، خلفية primary-50 للحروف.</t>
         </is>
@@ -5196,7 +5200,7 @@
           <t>public/website/css/front/dga-platforms-code.css §6</t>
         </is>
       </c>
-      <c r="I140" s="152" t="inlineStr">
+      <c r="I140" s="153" t="inlineStr">
         <is>
           <t>حقل الإدخال وفق كود المنصات.</t>
         </is>
@@ -5226,7 +5230,7 @@
         </is>
       </c>
       <c r="H141" s="35" t="n"/>
-      <c r="I141" s="152" t="inlineStr">
+      <c r="I141" s="153" t="inlineStr">
         <is>
           <t>ارتفاع 40px، حد 1px رمادي 400، حواف 4px، خط 16px، تسمية 14px وزن 500 فوق الحقل.</t>
         </is>
@@ -5252,7 +5256,7 @@
         </is>
       </c>
       <c r="H142" s="35" t="n"/>
-      <c r="I142" s="152" t="inlineStr">
+      <c r="I142" s="153" t="inlineStr">
         <is>
           <t>Default، Hover (حد 500)، Pressed/Focus (حد أسود + إطار)، Read-only، Disabled.</t>
         </is>
@@ -5279,7 +5283,7 @@
         </is>
       </c>
       <c r="H143" s="56" t="n"/>
-      <c r="I143" s="154" t="inlineStr">
+      <c r="I143" s="155" t="inlineStr">
         <is>
           <t>Placeholder رمادي 500، نص مساعد تحت الحقل، رسالة الخطأ بأيقونة ولون أحمر 700 مع حد الحقل أحمر وrole="alert".</t>
         </is>
@@ -5314,7 +5318,7 @@
           <t>public/website/css/front/dga-platforms-code.css §15</t>
         </is>
       </c>
-      <c r="I144" s="152" t="inlineStr">
+      <c r="I144" s="153" t="inlineStr">
         <is>
           <t>الجداول وفق كود المنصات.</t>
         </is>
@@ -5375,7 +5379,7 @@
           <t>public/website/js/dga-datepicker.js + public/website/css/front/dga-platforms-code.css §27</t>
         </is>
       </c>
-      <c r="I146" s="152" t="inlineStr">
+      <c r="I146" s="153" t="inlineStr">
         <is>
           <t>مكون محدد التاريخ وفق كود المنصات: حقل إدخال بزر تقويم، ونافذة تقويم منبثقة بشبكة الأيام وأزرار الشهر السابق/التالي وأزرار اليوم/مسح، مع دعم لوحة المفاتيح وقارئ الشاشة.</t>
         </is>
@@ -5405,7 +5409,7 @@
         </is>
       </c>
       <c r="H147" s="35" t="n"/>
-      <c r="I147" s="152" t="inlineStr">
+      <c r="I147" s="153" t="inlineStr">
         <is>
           <t>حقل التاريخ بنفس شكل حقل الإدخال (حد، حواف، ارتفاع).</t>
         </is>
@@ -5431,7 +5435,7 @@
         </is>
       </c>
       <c r="H148" s="35" t="n"/>
-      <c r="I148" s="152" t="inlineStr">
+      <c r="I148" s="153" t="inlineStr">
         <is>
           <t>Default، Hover، Pressed، Focus، Disabled.</t>
         </is>
@@ -5457,7 +5461,7 @@
         </is>
       </c>
       <c r="H149" s="56" t="n"/>
-      <c r="I149" s="154" t="inlineStr">
+      <c r="I149" s="155" t="inlineStr">
         <is>
           <t>Selected (خلفية أساسية ونص أبيض)، Today (إطار أساسي)، Next/Prev (أزرار 36px بحدود)، والأيام خارج النطاق Disabled.</t>
         </is>
@@ -5487,12 +5491,12 @@
           <t>تطبيق كلي</t>
         </is>
       </c>
-      <c r="H150" s="152" t="inlineStr">
+      <c r="H150" s="153" t="inlineStr">
         <is>
           <t>app/Application/views/website/sitemap.blade.php</t>
         </is>
       </c>
-      <c r="I150" s="152" t="inlineStr">
+      <c r="I150" s="153" t="inlineStr">
         <is>
           <t>خريطة الموقع متاحة على /sitemap ومرتبطة من التذييل.</t>
         </is>
@@ -5580,7 +5584,7 @@
         </is>
       </c>
       <c r="H153" s="35" t="n"/>
-      <c r="I153" s="152" t="inlineStr">
+      <c r="I153" s="153" t="inlineStr">
         <is>
           <t>تصميم التفاعل.</t>
         </is>
@@ -5606,7 +5610,7 @@
         </is>
       </c>
       <c r="H154" s="35" t="n"/>
-      <c r="I154" s="152" t="inlineStr">
+      <c r="I154" s="153" t="inlineStr">
         <is>
           <t>استجابات فورية: Hover/Pressed/Focus لكل الأزرار والروابط، وحالة Loading للأزرار.</t>
         </is>
@@ -5632,7 +5636,7 @@
         </is>
       </c>
       <c r="H155" s="35" t="n"/>
-      <c r="I155" s="152" t="inlineStr">
+      <c r="I155" s="153" t="inlineStr">
         <is>
           <t>التمرير، السحب في شرائط الشعارات، والنقر المطول مدعومة طبيعياً.</t>
         </is>
@@ -5689,7 +5693,7 @@
         </is>
       </c>
       <c r="H157" s="35" t="n"/>
-      <c r="I157" s="152" t="inlineStr">
+      <c r="I157" s="153" t="inlineStr">
         <is>
           <t>العربية هي اللغة الأساسية في جميع الصفحات، مع دعم الإنجليزية عبر مبدّل اللغة في الختم الرقمي.</t>
         </is>
@@ -5715,7 +5719,7 @@
         </is>
       </c>
       <c r="H158" s="35" t="n"/>
-      <c r="I158" s="152" t="inlineStr">
+      <c r="I158" s="153" t="inlineStr">
         <is>
           <t>العربية لغة أساسية لكل الصفحات والمكونات مع مراجعة الصياغة.</t>
         </is>
@@ -5741,7 +5745,7 @@
         </is>
       </c>
       <c r="H159" s="35" t="n"/>
-      <c r="I159" s="152" t="inlineStr">
+      <c r="I159" s="153" t="inlineStr">
         <is>
           <t>الإنجليزية ثانوية عبر LaravelLocalization (/en) مع ملفات ترجمة للواجهة.</t>
         </is>
@@ -5803,7 +5807,7 @@
         </is>
       </c>
       <c r="H161" s="35" t="n"/>
-      <c r="I161" s="152" t="inlineStr">
+      <c r="I161" s="153" t="inlineStr">
         <is>
           <t>آليات التغذية الراجعة.</t>
         </is>
@@ -5829,7 +5833,7 @@
         </is>
       </c>
       <c r="H162" s="35" t="n"/>
-      <c r="I162" s="152" t="inlineStr">
+      <c r="I162" s="153" t="inlineStr">
         <is>
           <t>نموذج التواصل، تقييم الدورة، ونموذج الملاحظات، مع رابط الدعم في الهيدر والتذييل.</t>
         </is>
@@ -5856,7 +5860,7 @@
         </is>
       </c>
       <c r="H163" s="56" t="n"/>
-      <c r="I163" s="154" t="inlineStr">
+      <c r="I163" s="155" t="inlineStr">
         <is>
           <t>رسالة تأكيد (Inline Alert / Toast) بعد الإرسال.</t>
         </is>
@@ -5887,7 +5891,7 @@
         </is>
       </c>
       <c r="H164" s="35" t="n"/>
-      <c r="I164" s="152" t="inlineStr">
+      <c r="I164" s="153" t="inlineStr">
         <is>
           <t>إشعارات الخصوصية والأمان.</t>
         </is>
@@ -5913,7 +5917,7 @@
         </is>
       </c>
       <c r="H165" s="35" t="n"/>
-      <c r="I165" s="152" t="inlineStr">
+      <c r="I165" s="153" t="inlineStr">
         <is>
           <t>سياسة الخصوصية وبيان إمكانية الوصول في التذييل والشريط السفلي، وشريط موافقة ملفات الارتباط في أول زيارة.</t>
         </is>
@@ -5939,7 +5943,7 @@
         </is>
       </c>
       <c r="H166" s="35" t="n"/>
-      <c r="I166" s="152" t="inlineStr">
+      <c r="I166" s="153" t="inlineStr">
         <is>
           <t>روابط الشروط والخصوصية في نماذج الدخول/التسجيل والتواصل.</t>
         </is>
@@ -5997,7 +6001,7 @@
         </is>
       </c>
       <c r="H168" s="35" t="n"/>
-      <c r="I168" s="152" t="inlineStr">
+      <c r="I168" s="153" t="inlineStr">
         <is>
           <t>توحيد المصطلحات.</t>
         </is>
@@ -6023,7 +6027,7 @@
         </is>
       </c>
       <c r="H169" s="35" t="n"/>
-      <c r="I169" s="152" t="inlineStr">
+      <c r="I169" s="153" t="inlineStr">
         <is>
           <t>مصطلحات موحدة: "ابدأ الخدمة"، "بحث"، "السابق/التالي"، "تسجيل الدخول/حساب جديد"، "التفاصيل" في كل الصفحات.</t>
         </is>
@@ -6049,7 +6053,7 @@
         </is>
       </c>
       <c r="H170" s="35" t="n"/>
-      <c r="I170" s="152" t="inlineStr">
+      <c r="I170" s="153" t="inlineStr">
         <is>
           <t>المصطلحات تعكس الوظيفة بدقة.</t>
         </is>
@@ -6132,7 +6136,7 @@
         </is>
       </c>
       <c r="H173" s="35" t="n"/>
-      <c r="I173" s="152" t="inlineStr">
+      <c r="I173" s="153" t="inlineStr">
         <is>
           <t>نهج ثابت للأخطاء.</t>
         </is>
@@ -6158,7 +6162,7 @@
         </is>
       </c>
       <c r="H174" s="35" t="n"/>
-      <c r="I174" s="152" t="inlineStr">
+      <c r="I174" s="153" t="inlineStr">
         <is>
           <t>رسائل الخطأ تحت الحقل بنفس النمط (أيقونة + نص أحمر 700 + حد الحقل أحمر) في جميع النماذج، وتنبيهات Inline Alert للأخطاء العامة.</t>
         </is>
@@ -6184,7 +6188,7 @@
         </is>
       </c>
       <c r="H175" s="35" t="n"/>
-      <c r="I175" s="152" t="inlineStr">
+      <c r="I175" s="153" t="inlineStr">
         <is>
           <t>صياغة موحدة: "الرجاء إدخال …" / "تم … بنجاح".</t>
         </is>

--- a/docs/dga/نموذج الالتزام - منصة الشهادات الاحترافية - جامعة شقراء.xlsx
+++ b/docs/dga/نموذج الالتزام - منصة الشهادات الاحترافية - جامعة شقراء.xlsx
@@ -1805,12 +1805,12 @@
       </c>
       <c r="H20" s="150" t="inlineStr">
         <is>
-          <t>public/website/js/dga-icons.js</t>
+          <t>app/Application/Helpers/dga-icons-map.php + public/website/js/dga-hgi-map.js</t>
         </is>
       </c>
       <c r="I20" s="153" t="inlineStr">
         <is>
-          <t>مكتبة أيقونات موحدة: جميع الأيقونات خطية SVG (stroke 2px) بأحجام 16/20/24px وبألوان محايدة، وألوان الحالات للتنبيهات فقط، والأيقونات الكبيرة بصيغة Featured icon (48px بخلفية خفيفة). طبقة dga-icons.js تستبدل أي أيقونة قديمة (Font Awesome) تلقائياً بأيقونة المكتبة الموحدة دون تغيير الحجم أو اللون.</t>
+          <t>مكتبة الأيقونات المعتمدة في كود المنصات (Hugeicons – Stroke Rounded)، وهي نفس المكتبة المستخدمة في موقع جامعة شقراء المعتمد من الهيئة (su.edu.sa). جميع الأيقونات تُرسم من المكتبة عبر الدالة dgaIcon() في القوالب، وطبقة dga-icons.js تستبدل أي أيقونة قديمة (Font Awesome) تلقائياً بأيقونة المكتبة نفسها بالأحجام 16/20/24px وبألوان محايدة، وألوان الحالات للتنبيهات فقط.</t>
         </is>
       </c>
       <c r="J20" s="152" t="inlineStr">
@@ -1841,7 +1841,7 @@
       <c r="H21" s="131" t="n"/>
       <c r="I21" s="153" t="inlineStr">
         <is>
-          <t>مكتبة أيقونات واحدة (SVG خطية) في كل الصفحات؛ لم يتبقَّ أي استخدام لخط الأيقونات القديم في واجهات الزائر (تم التحقق آلياً: 0 عنصر Font Awesome بعد التحميل).</t>
+          <t>مكتبة واحدة (Hugeicons) في كل الصفحات دون تعديل في الشكل أو السماكة (1.5px) أو اللون؛ تم التحقق آلياً على 28 صفحة: 0 عنصر Font Awesome و0 أيقونات مخصصة بعد التحميل.</t>
         </is>
       </c>
       <c r="J21" s="94" t="n"/>
